--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -771,7 +771,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -782,15 +782,24 @@
         </is>
       </c>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
@@ -798,16 +807,21 @@
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="n"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
+</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
@@ -819,13 +833,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
@@ -863,18 +877,27 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4380</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -883,19 +906,15 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">99
+211
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -907,13 +926,13 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -925,7 +944,8 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -936,7 +956,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
@@ -998,7 +1018,7 @@
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1010,7 +1030,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -1028,43 +1048,40 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1725
+          <t xml:space="preserve">16495171
+178
+2 2 4221
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1082,7 +1099,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>083</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1092,31 +1109,31 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -1141,24 +1158,20 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2744
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1170,7 +1183,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1188,7 +1201,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1200,25 +1213,25 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8821
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1230,7 +1243,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">2287
 </t>
         </is>
       </c>
@@ -1266,7 +1279,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1278,7 +1291,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1297,25 +1310,25 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602
+          <t xml:space="preserve">16024
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1339,49 +1352,39 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">093
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118628
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8821
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2465
-</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1398,13 +1401,13 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -1426,8 +1429,18 @@
 </t>
         </is>
       </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1443,34 +1456,21 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16024
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
@@ -1488,54 +1488,53 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8145
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">1271
+</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>710</t>
         </is>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
+          <t xml:space="preserve">3892
 </t>
         </is>
       </c>
@@ -1547,7 +1546,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -1559,21 +1558,16 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1589,74 +1583,69 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
+          <t xml:space="preserve">1464
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">4465227
+8179171
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
+          <t xml:space="preserve">2282891
+181
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">82828
+199812
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792871272
+1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">94
+2
 </t>
         </is>
       </c>
@@ -1668,63 +1657,40 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7424
+1111
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">845
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4451
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1740,31 +1706,15 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1661
-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
+          <t>4985</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1776,73 +1726,49 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">77718
+6222
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">231
+24721195
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1854,31 +1780,31 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1865
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">8960
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1897,7 +1823,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -1920,78 +1846,69 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">977
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">2911
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -2009,19 +1926,19 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
@@ -2033,7 +1950,8 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2081,7 +1999,8 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">159
+1109
 </t>
         </is>
       </c>
@@ -2093,32 +2012,32 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2142,7 +2061,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2154,7 +2073,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2166,13 +2085,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2219
 </t>
         </is>
       </c>
@@ -2203,13 +2122,14 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2238
+          <t xml:space="preserve">3238
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2218,67 +2138,49 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29225
-</t>
-        </is>
-      </c>
+      <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>051</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1771
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2290,18 +2192,19 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -2325,16 +2228,11 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">09
@@ -2356,7 +2254,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
@@ -2372,75 +2270,55 @@
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1714
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+          <t xml:space="preserve">2324
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">896
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2410
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -2453,7 +2331,7 @@
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2471,12 +2349,13 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">958
+</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2501,7 +2380,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89348
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -2519,13 +2398,13 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2547,20 +2426,16 @@
 </t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -2572,42 +2447,38 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2291
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">414
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">21214
+7922
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -2625,7 +2496,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2637,8 +2508,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2654,76 +2524,62 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>156468</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1099
-</t>
-        </is>
-      </c>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>060</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>865594</t>
-        </is>
-      </c>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
           <t>614</t>
@@ -2731,32 +2587,26 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">744
+981
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3591
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
@@ -2767,18 +2617,18 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
-</t>
+          <t>96121</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">8203
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2804,51 +2654,47 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917
+          <t xml:space="preserve">9917
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2971
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>446</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">30
 </t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -2857,19 +2703,18 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>85341</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2881,24 +2726,19 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
@@ -2910,25 +2750,25 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6574
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2951,12 +2791,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12534
-</t>
-        </is>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>33</t>
@@ -2970,36 +2805,31 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">77718
+273
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>0164</t>
-        </is>
-      </c>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -3011,18 +2841,14 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -3046,7 +2872,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3058,40 +2884,35 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2691
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">15
 </t>
         </is>
       </c>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3105,40 +2926,35 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1621
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">5454824
 </t>
         </is>
       </c>
@@ -3162,25 +2978,25 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3192,49 +3008,44 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2685
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">2341
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -3259,72 +3070,66 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12534
+          <t xml:space="preserve">2534
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>0164</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">828127
+160
+745414119
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3335,7 +3140,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -3353,13 +3158,14 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">26
+1 1
 </t>
         </is>
       </c>
@@ -3371,25 +3177,25 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1991
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">736
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3414,7 +3220,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53349
+          <t xml:space="preserve">2661
 </t>
         </is>
       </c>
@@ -3426,42 +3232,33 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92925
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">44282
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">23
+77
 </t>
         </is>
       </c>
@@ -3473,13 +3270,13 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3491,7 +3288,8 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
+2
 </t>
         </is>
       </c>
@@ -3507,39 +3305,31 @@
 </t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">449
+190
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8232
+          <t xml:space="preserve">124
+1856
 </t>
         </is>
       </c>
@@ -3570,7 +3360,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15486
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -3588,38 +3378,28 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">3106
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>6163</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -3628,49 +3408,49 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2512
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3931
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
@@ -3688,7 +3468,8 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">449
+190
 </t>
         </is>
       </c>
@@ -3725,139 +3506,116 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>309</t>
+          <t xml:space="preserve">586
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11159
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>572</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t xml:space="preserve">491
+</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>633</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>371</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">008
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3873,7 +3631,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -3885,65 +3643,65 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
+          <t xml:space="preserve">1791
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9380
+          <t xml:space="preserve">381
 </t>
         </is>
       </c>
@@ -3961,18 +3719,19 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>644</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -3984,31 +3743,26 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">750
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="n"/>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4027,137 +3781,112 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">2798
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+          <t>948</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9146
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t>016</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">18020
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -4182,7 +3911,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
@@ -4194,60 +3923,62 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">792
+67
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t xml:space="preserve">12
+1119
+</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4259,61 +3990,60 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -4338,7 +4068,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
@@ -4350,60 +4080,47 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">792
+67
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">167
 </t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2817
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">707
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4415,66 +4132,67 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2181
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7467
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
-</t>
-        </is>
-      </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">83836
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4493,25 +4211,21 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">4536
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4007
+263
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">8414
 </t>
         </is>
       </c>
@@ -4523,12 +4237,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">331
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4540,7 +4254,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -4552,20 +4266,20 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">6041
+151
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>05840</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4582,49 +4296,49 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">17272
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">747
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0612
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">752
 </t>
         </is>
       </c>
@@ -4649,37 +4363,36 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t xml:space="preserve">3436
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4696,7 +4409,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4708,48 +4421,48 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t xml:space="preserve">865
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4760,25 +4473,25 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>881</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4802,13 +4515,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23577
+          <t xml:space="preserve">17884
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4820,25 +4533,25 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451111
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4850,7 +4563,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">2 3
 </t>
         </is>
       </c>
@@ -4862,49 +4575,42 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2018
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>85431</t>
+          <t xml:space="preserve">45845
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1 48
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>018</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
@@ -4915,31 +4621,29 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>002</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4957,13 +4661,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4975,89 +4679,88 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">24
+77
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+777
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16811
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">491
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9780
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5069,31 +4772,26 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -5112,25 +4810,25 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5152,18 +4850,8 @@
 </t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1297
-</t>
-        </is>
-      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -5172,7 +4860,8 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">157
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -5183,73 +4872,73 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">9461
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5268,13 +4957,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12502
+          <t xml:space="preserve">4068
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5286,43 +4975,39 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">7777
+262
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5334,7 +5019,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5346,61 +5031,61 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -5425,7 +5110,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -5443,13 +5128,13 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -5461,83 +5146,78 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>001</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8200
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1837
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">2198
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5549,7 +5229,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
@@ -5561,7 +5241,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5580,7 +5260,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3568
+          <t xml:space="preserve">4688
 </t>
         </is>
       </c>
@@ -5592,35 +5272,37 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5632,88 +5314,76 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">8006
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="n"/>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">602
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2808
-</t>
-        </is>
-      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5731,30 +5401,27 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t xml:space="preserve">358
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>083</t>
-        </is>
-      </c>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t>806</t>
@@ -5762,96 +5429,91 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>9611</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">991
-</t>
-        </is>
-      </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">038
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="n"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">981
+2248
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">77
+181 1
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5876,32 +5538,31 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">6432
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">9637
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>085</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5912,71 +5573,68 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5247
+2272
+1
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="n"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -5988,23 +5646,19 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10921
+          <t xml:space="preserve">14441
+346
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="n"/>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6020,52 +5674,48 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1
+1 23
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -6074,53 +5724,49 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">171
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n"/>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -6132,7 +5778,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
@@ -6148,12 +5794,7 @@
 </t>
         </is>
       </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -6181,100 +5822,82 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">2852
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">21626
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">231 1
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -6304,7 +5927,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -6323,7 +5946,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
@@ -6335,65 +5958,57 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>015</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">196
+111
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1177
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -6405,31 +6020,29 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1951
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6447,13 +6060,13 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">705
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6478,80 +6091,82 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">3590
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n"/>
+          <t xml:space="preserve">2135
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29
+2
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n"/>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">9271249
+157
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -6563,22 +6178,17 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="n"/>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -6587,13 +6197,13 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">9134
 </t>
         </is>
       </c>
@@ -6603,7 +6213,12 @@
 </t>
         </is>
       </c>
-      <c r="Z42" s="3" t="n"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6619,13 +6234,14 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t xml:space="preserve">276
+</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6636,93 +6252,116 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5925
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">697
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11615
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="n"/>
+          <t xml:space="preserve">711797
+127
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+118
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n"/>
+          <t xml:space="preserve">2031
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>777</t>
+          <t xml:space="preserve">555
+</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
+          <t xml:space="preserve">216868
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="n"/>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6738,26 +6377,32 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">24
+60292929572
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n"/>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1577
+</t>
+        </is>
+      </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5925
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -6769,103 +6414,90 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">1642
+24749414
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">99
+118
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">727
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">7773
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65566
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="n"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -6885,13 +6517,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3679
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6903,13 +6534,14 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">1791287
+</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -6920,19 +6552,19 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6944,11 +6576,17 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="n"/>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">811
@@ -6957,55 +6595,61 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>521</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">2628
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4224574
+1
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="n"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7025,84 +6669,123 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817857
+1 1
+1
+3
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">526
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+1
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -726,43 +726,41 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23898
+</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">55
@@ -771,42 +769,51 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0168
+</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">851
@@ -821,7 +828,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">28208
 </t>
         </is>
       </c>
@@ -833,13 +840,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
@@ -862,7 +869,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14286
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
@@ -877,27 +889,23 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>4380</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -906,15 +914,14 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-211
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -926,38 +933,37 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1931
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">12248
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">013
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">111012
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -974,8 +980,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -1018,19 +1023,19 @@
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">8261
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
@@ -1042,49 +1047,42 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16495171
-178
-2 2 4221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1093,41 +1091,42 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">2203
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>783</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>64</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -1156,22 +1155,22 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">0202
 </t>
         </is>
       </c>
@@ -1183,7 +1182,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1201,85 +1200,65 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1279
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1698
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1729
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2287
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1291,7 +1270,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1308,33 +1287,28 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16024
-</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -1352,68 +1326,69 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n"/>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1082
+</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>4451</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1212
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
+      <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1096
 </t>
         </is>
       </c>
@@ -1437,7 +1412,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1454,24 +1429,19 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16024
-</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">2598
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">627
-</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1482,36 +1452,31 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>310</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">342201
 </t>
         </is>
       </c>
@@ -1520,54 +1485,41 @@
           <t>24</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1271
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3892
+          <t xml:space="preserve">3842
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19385
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9271031
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+          <t xml:space="preserve">194451
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1583,114 +1535,78 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464
-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4465227
-8179171
-</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2282891
-181
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4281
+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82828
-199812
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">792871272
-1
-</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">784
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8220171
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-2
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9061
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7424
-1111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
-      <c r="U10" s="3" t="n"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
       <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4451
-</t>
-        </is>
-      </c>
+      <c r="W10" s="3" t="n"/>
+      <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1706,105 +1622,129 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4985</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+          <t xml:space="preserve">12996
+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
+          <t xml:space="preserve">2217
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77718
-6222
-</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-24721195
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2290
+</t>
+        </is>
+      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1865
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8960
-</t>
-        </is>
-      </c>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1823,134 +1763,138 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">23436
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2911
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1036
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">845
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1969,19 +1913,19 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">23238
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -1991,119 +1935,107 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-1109
-</t>
-        </is>
-      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2164
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1994
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -2122,101 +2054,105 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3238
+          <t xml:space="preserve">2600
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1771
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">1958
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2228,14 +2164,14 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2254,114 +2190,130 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">23348
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="n"/>
+          <t xml:space="preserve">1017
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10914
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2214
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="n"/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1993
+</t>
+        </is>
+      </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="n"/>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -2380,135 +2332,123 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">101618
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1348
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1099
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">14814
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n"/>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118126
+</t>
+        </is>
+      </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>86531</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>1584</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21214
-7922
-</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">133591
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">11018
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">4574
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2527,111 +2467,65 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n"/>
+          <t xml:space="preserve">19113
+</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>060</t>
+          <t xml:space="preserve">8171
+</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
+      <c r="P17" s="3" t="n"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">744
-981
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>7556</t>
-        </is>
-      </c>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="U17" s="3" t="n"/>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>96121</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8203
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="n"/>
+      <c r="Y17" s="3" t="n"/>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2648,133 +2542,114 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">9546
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917
+          <t xml:space="preserve">2209
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1082
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>85341</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="n"/>
+          <t xml:space="preserve">1267
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1851
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1239
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="n"/>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1097
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1069
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="n"/>
+      <c r="X18" s="3" t="n"/>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2794,125 +2669,116 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77718
-273
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">089
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="n"/>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2929,129 +2795,103 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5454824
-</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2685
-</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341
-</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="n"/>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -3070,138 +2910,113 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534
+          <t xml:space="preserve">12848
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828127
-160
-745414119
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-1 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">2262
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1991
+          <t xml:space="preserve">0206
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>961</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3220,45 +3035,55 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2661
+          <t xml:space="preserve">23392
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44282
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-77
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3270,46 +3095,49 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1171
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-2
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="n"/>
-      <c r="T22" s="3" t="n"/>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -3321,27 +3149,25 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-1856
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3358,139 +3184,91 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">392
-</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3106
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n"/>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">748
+</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">11212
+</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n"/>
+          <t xml:space="preserve">1699
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">14691
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2512
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">3938
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">23992
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449
-190
-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1103
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="n"/>
+      <c r="X23" s="3" t="n"/>
+      <c r="Y23" s="3" t="n"/>
+      <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3506,116 +3284,135 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">586
+          <t xml:space="preserve">23097
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">247
+</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t xml:space="preserve">1174
+</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t xml:space="preserve">1188
+</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">491
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t xml:space="preserve">121
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t xml:space="preserve">1200
+</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>752</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>371</t>
+          <t xml:space="preserve">47
+</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="n"/>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7130
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">163
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="n"/>
-      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3629,140 +3426,137 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1791
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>984</t>
+          <t xml:space="preserve">895
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">381
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="n"/>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3781,118 +3575,119 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>948</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">395
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1611
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="n"/>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="n"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18020
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="n"/>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2141
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3911,145 +3706,119 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">14536
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">792
-67
-</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-1119
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">12068
+</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1878
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n"/>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">785
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -4068,107 +3837,111 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
+          <t xml:space="preserve">23436
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">792
-67
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
+          <t xml:space="preserve">11160
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n"/>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">12920
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">238116
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="n"/>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
@@ -4180,19 +3953,19 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83836
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4211,143 +3984,101 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4536
+          <t xml:space="preserve">17884
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007
-263
+          <t xml:space="preserve">1584
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8414
-</t>
-        </is>
-      </c>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">1630
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6041
-151
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>05840</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17272
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="n"/>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">747
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">9300
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">752
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">120080
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -4361,145 +4092,50 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3436
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
-</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80101
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2280
-</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="T30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="U30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101811
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="3" t="n"/>
+      <c r="U30" s="3" t="n"/>
+      <c r="V30" s="3" t="n"/>
+      <c r="W30" s="3" t="n"/>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n"/>
+      <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4515,135 +4151,130 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17884
+          <t xml:space="preserve">12666
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2867
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1822
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 3
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n"/>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45845
+          <t xml:space="preserve">7920
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">010
+</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 48
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>018</t>
+          <t xml:space="preserve">1180
+</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">980
+</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">19406
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>002</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4661,137 +4292,105 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14008
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-77
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-777
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">909
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="n"/>
+      <c r="R32" s="3" t="n"/>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">491
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">2794
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="n"/>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="n"/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -4810,135 +4409,105 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">13502
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1256
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2018
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="n"/>
+      <c r="X33" s="3" t="n"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9461
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2938
 </t>
         </is>
       </c>
@@ -4957,144 +4526,98 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068
-</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12688
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">417
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7777
-262
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1201
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="n"/>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -5110,138 +4633,110 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">13568
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1837
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="n"/>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">267
+</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">068
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1602
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="n"/>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5258,134 +4753,100 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4688
-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">11071
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">485
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">17106
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">11667
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">1606
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n"/>
+          <t xml:space="preserve">883
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8006
+          <t xml:space="preserve">182980
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="n"/>
+      <c r="R36" s="3" t="n"/>
+      <c r="S36" s="3" t="n"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="n"/>
+          <t xml:space="preserve">208594
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1342
+</t>
+        </is>
+      </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2981
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="n"/>
+      <c r="X36" s="3" t="n"/>
+      <c r="Y36" s="3" t="n"/>
+      <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5399,130 +4860,80 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>883</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">7961
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="T37" s="3" t="n"/>
       <c r="U37" s="3" t="n"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-2248
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-181 1
+          <t xml:space="preserve">2061
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5538,127 +4949,107 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6432
+          <t xml:space="preserve">122644
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9637
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>085</t>
-        </is>
-      </c>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5247
-2272
-1
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="n"/>
+          <t xml:space="preserve">1298
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2397
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="n"/>
+      <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14441
-346
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">1059
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="n"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2114
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5674,127 +5065,126 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">12864
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-1 23
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">971
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n"/>
+          <t xml:space="preserve">807
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1877
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">744
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="n"/>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="n"/>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1181
-</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1851
-</t>
-        </is>
-      </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="n"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -5810,127 +5200,118 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644
+          <t xml:space="preserve">123590
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n"/>
       <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n"/>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21626
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231 1
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2012
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Z40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="n"/>
+      <c r="Z40" s="3" t="n"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -5946,100 +5327,72 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
+          <t xml:space="preserve">14866
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-111
-</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1146
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1177
+</t>
+        </is>
+      </c>
       <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">766
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1951
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>7444</t>
-        </is>
-      </c>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="n"/>
       <c r="U41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -6054,28 +5407,18 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="n"/>
+      <c r="Z41" s="3" t="n"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6091,100 +5434,89 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">19426
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-2
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9271249
-157
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1801
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n"/>
+      <c r="O42" s="3" t="n"/>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -6197,28 +5529,23 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9134
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6232,136 +5559,93 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="n"/>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697
+</t>
+        </is>
+      </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2681
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711797
-127
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">796
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">12055
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">555
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216868
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n"/>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n"/>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1048
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="n"/>
       <c r="X43" s="3" t="n"/>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6375,132 +5659,29 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-60292929572
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">773
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1577
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">697
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1642
-24749414
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1878
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-118
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">727
-</t>
-        </is>
-      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
+      <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="n"/>
       <c r="Q44" s="3" t="n"/>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">728
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7773
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">028
-</t>
-        </is>
-      </c>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
+      <c r="U44" s="3" t="n"/>
       <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6517,76 +5698,55 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">23689
+</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1791287
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-1
-</t>
-        </is>
-      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">811
@@ -6595,64 +5755,29 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">299
+</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2628
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4224574
-1
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="n"/>
+      <c r="T45" s="3" t="n"/>
+      <c r="U45" s="3" t="n"/>
+      <c r="V45" s="3" t="n"/>
+      <c r="W45" s="3" t="n"/>
+      <c r="X45" s="3" t="n"/>
+      <c r="Y45" s="3" t="n"/>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -6667,128 +5792,49 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817857
-1 1
-1
-3
-6
-</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">526
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
       <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
+      <c r="U46" s="3" t="n"/>
+      <c r="V46" s="3" t="n"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-1
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8110
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -728,13 +728,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23898
+          <t xml:space="preserve">3898
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -746,21 +746,28 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">55
@@ -769,24 +776,26 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t xml:space="preserve">1885
+</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -797,7 +806,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -809,11 +818,16 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">851
@@ -828,7 +842,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28208
+          <t xml:space="preserve">8203
 </t>
         </is>
       </c>
@@ -846,13 +860,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
@@ -871,13 +885,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14286
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -889,23 +903,28 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">2060
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n"/>
+          <t xml:space="preserve">2214 4
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -914,14 +933,19 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -933,42 +957,43 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">013
+          <t xml:space="preserve">1213
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111012
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">843
+</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -980,7 +1005,8 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -995,12 +1021,7 @@
 </t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1023,19 +1044,19 @@
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8261
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1047,32 +1068,37 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">098
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="n"/>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1651
 </t>
         </is>
       </c>
@@ -1082,7 +1108,12 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1091,7 +1122,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1103,7 +1134,8 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">690
+</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1120,13 +1152,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1138,7 +1170,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1155,10 +1187,15 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2744
+</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">2542
 </t>
         </is>
       </c>
@@ -1170,14 +1207,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0202
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1192,28 +1227,28 @@
 </t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1229,21 +1264,36 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="n"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1882
+</t>
+        </is>
+      </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
         </is>
       </c>
-      <c r="S7" s="3" t="n"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1208
@@ -1252,7 +1302,7 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1270,7 +1320,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1287,7 +1337,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12602
+</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -1302,13 +1357,13 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">2271
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -1326,13 +1381,13 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -1350,7 +1405,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">1692
 </t>
         </is>
       </c>
@@ -1362,21 +1417,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="S8" s="3" t="n"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -1388,7 +1453,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
@@ -1429,30 +1494,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8291
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2598
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t xml:space="preserve">617
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
@@ -1464,7 +1550,8 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t xml:space="preserve">818
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1473,21 +1560,42 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2123
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342201
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4124
+</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1496,21 +1604,31 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19385
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="n"/>
+          <t xml:space="preserve">0285
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9289
+</t>
+        </is>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9271031
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11201
+</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194451
+          <t xml:space="preserve">94451
 </t>
         </is>
       </c>
@@ -1539,71 +1657,135 @@
 </t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">111 8
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11411
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220171
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28211
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9061
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+          <t xml:space="preserve">1254
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">628
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">77
 </t>
         </is>
       </c>
-      <c r="V10" s="3" t="n"/>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
       <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="3" t="n"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2151
 </t>
         </is>
       </c>
@@ -1622,13 +1804,13 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12996
+          <t xml:space="preserve">2996
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -1640,7 +1822,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1652,67 +1834,73 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t xml:space="preserve">1192
+</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -1724,27 +1912,37 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1763,7 +1961,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">03436
 </t>
         </is>
       </c>
@@ -1775,19 +1973,19 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -1805,13 +2003,13 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1829,24 +2027,25 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1036
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -1858,12 +2057,13 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1875,26 +2075,31 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="n"/>
+          <t xml:space="preserve">2129
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1913,7 +2118,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23238
+          <t xml:space="preserve">293238
 </t>
         </is>
       </c>
@@ -1935,24 +2140,35 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">877
+</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1963,7 +2179,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -1973,15 +2189,10 @@
 </t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
-</t>
-        </is>
-      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -1999,7 +2210,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -2017,7 +2228,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -2029,13 +2240,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">958
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -2054,8 +2265,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
-</t>
+          <t>86004</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2066,17 +2276,28 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">914
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -2085,26 +2306,31 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -2116,13 +2342,13 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -2140,13 +2366,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2164,14 +2390,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="n"/>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2190,7 +2421,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23348
+          <t xml:space="preserve">9348
 </t>
         </is>
       </c>
@@ -2208,39 +2439,49 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10914
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2258,19 +2499,19 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -2282,26 +2523,31 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993
+          <t xml:space="preserve">9953
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="n"/>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">2023
 </t>
         </is>
       </c>
@@ -2313,7 +2559,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2332,13 +2578,13 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101618
+          <t xml:space="preserve">02688
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1348
+          <t xml:space="preserve">14281
 </t>
         </is>
       </c>
@@ -2356,13 +2602,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14814
+          <t xml:space="preserve">4814
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">1908
 </t>
         </is>
       </c>
@@ -2374,13 +2620,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118126
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -2390,40 +2636,63 @@
 </t>
         </is>
       </c>
-      <c r="M16" s="3" t="n"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>86531</t>
+          <t xml:space="preserve">14659
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0169
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3114
+</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t xml:space="preserve">99208
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133591
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11018
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
@@ -2435,13 +2704,13 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">1087
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4574
+          <t xml:space="preserve">46584
 </t>
         </is>
       </c>
@@ -2464,54 +2733,114 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3124
+</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">8816
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19113
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8171
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">120117
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
         </is>
       </c>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="n"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2691
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2298
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7884
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -2520,13 +2849,28 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="n"/>
-      <c r="Y17" s="3" t="n"/>
-      <c r="Z17" s="3" t="n"/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2542,19 +2886,20 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9546
+          <t xml:space="preserve">29546
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">2771
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2571,79 +2916,109 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">2868
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1883
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141487
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1267
 </t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2128
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="n"/>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1247
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1069
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="3" t="n"/>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -2666,7 +3041,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">274
@@ -2681,22 +3061,37 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">8288
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -2708,13 +3103,13 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">089
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2726,7 +3121,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -2744,23 +3139,34 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="n"/>
+          <t xml:space="preserve">2080
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="n"/>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -2769,13 +3175,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">736
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -2792,7 +3198,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">534
+</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -2801,28 +3212,49 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0219
+</t>
+        </is>
+      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2834,14 +3266,19 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2863,10 +3300,14 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="3" t="n"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -2876,10 +3317,15 @@
 </t>
         </is>
       </c>
-      <c r="W20" s="3" t="n"/>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -2891,7 +3337,7 @@
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2910,19 +3356,20 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12848
+          <t xml:space="preserve">18246
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">2018
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -2931,24 +3378,39 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1711
+</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">1680
 </t>
         </is>
       </c>
@@ -2958,8 +3420,18 @@
 </t>
         </is>
       </c>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -2980,26 +3452,31 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="n"/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
+</t>
+        </is>
+      </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0206
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3011,12 +3488,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>961</t>
+          <t xml:space="preserve">968
+</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3035,7 +3513,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23392
+          <t xml:space="preserve">3392
 </t>
         </is>
       </c>
@@ -3059,47 +3537,52 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">106 2
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -3108,13 +3591,14 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -3131,7 +3615,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -3143,13 +3627,13 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">12190
 </t>
         </is>
       </c>
@@ -3167,7 +3651,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3184,36 +3668,57 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11212
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1699
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3224,51 +3729,83 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>8894</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14691
+          <t xml:space="preserve">2691
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81158
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3938
+          <t xml:space="preserve">2991
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23992
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
-      <c r="Y23" s="3" t="n"/>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">1100
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1996
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2100
+</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4068
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3290,126 +3827,129 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1701
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">18 051
+</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">2541
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
+          <t xml:space="preserve">1741
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">9381
+</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2391
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">2101
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2321
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="n"/>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7130
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211834
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="n"/>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3426,101 +3966,110 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2798
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
@@ -3532,31 +4081,31 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3575,119 +4124,145 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8253
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">167
 </t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">395
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1611
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1828
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2416
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3706,119 +4281,142 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14536
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12068
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1878
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="3" t="n"/>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>6364</t>
+        </is>
+      </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">062
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n"/>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3837,135 +4435,143 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">4536
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11160
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">933
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="n"/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12920
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238116
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">785
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3984,101 +4590,138 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17884
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">619
+</t>
+        </is>
+      </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>4545</t>
-        </is>
-      </c>
+      <c r="O29" s="3" t="n"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120080
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="n"/>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -4092,50 +4735,145 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1869
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80101
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">817
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
+          <t xml:space="preserve">7009
+</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8939
+</t>
+        </is>
+      </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101811
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 10
+</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14249
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
       <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81094
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2222
+</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
+          <t xml:space="preserve">9998
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1161
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4151,129 +4889,140 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12666
+          <t xml:space="preserve">23577
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">12862
+</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2867
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">111001
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">9 9
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n"/>
+          <t xml:space="preserve">11721
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101208101
+</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7920
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">12 66
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2191
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">611
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">1841
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19406
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">401
 </t>
         </is>
       </c>
@@ -4292,105 +5041,145 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n"/>
+          <t xml:space="preserve">2666
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n"/>
+          <t xml:space="preserve">1894
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1856
+</t>
+        </is>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">12064
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2794
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n"/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">0081
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4409,105 +5198,145 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13502
-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n"/>
+          <t xml:space="preserve">14008
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="n"/>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184
+</t>
+        </is>
+      </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">774
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
+          <t xml:space="preserve">1896
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2938
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -4526,98 +5355,147 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12688
-</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n"/>
+          <t xml:space="preserve">23502
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1156
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="n"/>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -4633,67 +5511,95 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13568
-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n"/>
+          <t xml:space="preserve">2688
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">40
 </t>
         </is>
       </c>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">790
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4705,38 +5611,43 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">892
+</t>
+        </is>
+      </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2441
 </t>
         </is>
       </c>
@@ -4753,100 +5664,145 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3568
+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11071
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17106
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11667
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182980
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" s="3" t="n"/>
-      <c r="S36" s="3" t="n"/>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208594
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2981
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n"/>
-      <c r="Y36" s="3" t="n"/>
-      <c r="Z36" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -4860,76 +5816,135 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16402
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16211
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13011
+</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">485
+</t>
+        </is>
+      </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1067
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16006
+</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1808
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1461
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="n"/>
-      <c r="U37" s="3" t="n"/>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1942
+</t>
+        </is>
+      </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2061
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9212
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">44817
 </t>
         </is>
       </c>
@@ -4947,109 +5962,135 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122644
-</t>
-        </is>
-      </c>
+      <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">2631
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
+          <t xml:space="preserve">8661
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">971
+</t>
+        </is>
+      </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1231
+</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n"/>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">7961
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">2122
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">117 8
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397
-</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="n"/>
-      <c r="U38" s="3" t="n"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7711
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1464
+</t>
+        </is>
+      </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1059
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2086
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5065,13 +6106,14 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12864
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5082,7 +6124,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5095,7 +6137,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5113,25 +6155,26 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
+          <t xml:space="preserve">1077
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -5143,13 +6186,13 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -5162,7 +6205,7 @@
       <c r="U39" s="3" t="n"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5172,19 +6215,9 @@
 </t>
         </is>
       </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
+      <c r="X39" s="3" t="n"/>
       <c r="Y39" s="3" t="n"/>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
+      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -5200,7 +6233,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123590
+          <t xml:space="preserve">53590
 </t>
         </is>
       </c>
@@ -5212,59 +6245,69 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">01116
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1138
 </t>
         </is>
       </c>
-      <c r="I40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5294,7 +6337,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5306,12 +6349,22 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="n"/>
-      <c r="Z40" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -5327,8 +6380,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14866
-</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5337,24 +6389,29 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1146
-</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="n"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5366,14 +6423,34 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="3" t="n"/>
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5392,10 +6469,15 @@
 </t>
         </is>
       </c>
-      <c r="T41" s="3" t="n"/>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5405,20 +6487,25 @@
 </t>
         </is>
       </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="W41" s="3" t="n"/>
       <c r="X41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="Y41" s="3" t="n"/>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -5434,7 +6521,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
+          <t xml:space="preserve">9426
 </t>
         </is>
       </c>
@@ -5444,10 +6531,15 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="3" t="n"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">2019
 </t>
         </is>
       </c>
@@ -5459,46 +6551,56 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">2841
 </t>
         </is>
       </c>
@@ -5510,17 +6612,22 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">8299
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n"/>
+          <t xml:space="preserve">555
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -5535,17 +6642,22 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">71
 </t>
         </is>
       </c>
-      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -5560,50 +6672,57 @@
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">8109
+</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">1081
+</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">0914
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -5616,32 +6735,67 @@
       <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12055
+          <t xml:space="preserve">1055
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
-      <c r="U43" s="3" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1251
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16 16
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536
+</t>
+        </is>
+      </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1048
 </t>
         </is>
       </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2193
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201 10
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">4 067
 </t>
         </is>
       </c>
@@ -5659,7 +6813,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -5698,7 +6857,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23689
+          <t xml:space="preserve">3629
 </t>
         </is>
       </c>
@@ -5710,19 +6869,25 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5738,12 +6903,27 @@
 </t>
         </is>
       </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 9
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -5755,29 +6935,64 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
-      <c r="U45" s="3" t="n"/>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -5793,47 +7008,122 @@
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n"/>
+          <t xml:space="preserve">014
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14107
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8110
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -734,13 +734,13 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -752,16 +752,16 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">125
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">38
@@ -776,13 +776,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -806,7 +806,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -824,7 +824,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8203
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
@@ -866,8 +866,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -885,14 +884,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">94326
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -909,13 +907,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
+          <t xml:space="preserve">02150
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214 4
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
@@ -933,7 +931,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -945,7 +943,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">0176
 </t>
         </is>
       </c>
@@ -957,7 +955,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -975,7 +973,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -987,7 +985,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -1080,7 +1078,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -1092,22 +1090,17 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
@@ -1189,13 +1182,13 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2744
+          <t xml:space="preserve">3844
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2542
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -1207,12 +1200,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1227,7 +1222,11 @@
 </t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1248,14 +1247,13 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1266,7 +1264,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1284,7 +1282,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
@@ -1296,7 +1294,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -1339,7 +1337,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12602
+          <t xml:space="preserve">2602
 </t>
         </is>
       </c>
@@ -1357,7 +1355,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2271
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1381,79 +1379,79 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1672
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">882
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">39
 </t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1692
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1496,37 +1494,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>34405</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">18248
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -1538,19 +1535,19 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -1562,13 +1559,13 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2123
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1586,16 +1583,11 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">0912
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1604,13 +1596,13 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0285
+          <t xml:space="preserve">385
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9289
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -1622,19 +1614,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11201
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94451
+          <t xml:space="preserve">4458
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -1659,7 +1651,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">2891
 </t>
         </is>
       </c>
@@ -1671,54 +1663,52 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 8
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">2821
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28211
+          <t xml:space="preserve">16878
 </t>
         </is>
       </c>
@@ -1730,25 +1720,25 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1766,7 +1756,7 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">1981
 </t>
         </is>
       </c>
@@ -1785,7 +1775,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1816,62 +1806,60 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">8311
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1882,7 +1870,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
@@ -1894,13 +1882,13 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -1918,7 +1906,7 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -1930,7 +1918,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1961,7 +1949,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03436
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
@@ -1973,13 +1961,13 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2009,7 +1997,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -2033,19 +2021,19 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -2057,13 +2045,12 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>086</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9230
 </t>
         </is>
       </c>
@@ -2087,7 +2074,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2099,7 +2086,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2118,7 +2105,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293238
+          <t xml:space="preserve">23238
 </t>
         </is>
       </c>
@@ -2130,7 +2117,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -2161,34 +2148,29 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -2210,7 +2192,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -2222,19 +2204,19 @@
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
@@ -2265,7 +2247,8 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>86004</t>
+          <t xml:space="preserve">2600
+</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2288,13 +2271,13 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -2306,7 +2289,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
@@ -2318,19 +2301,19 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">4189
 </t>
         </is>
       </c>
@@ -2342,7 +2325,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2372,7 +2355,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2396,7 +2379,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -2421,7 +2404,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9348
+          <t xml:space="preserve">2348
 </t>
         </is>
       </c>
@@ -2439,25 +2422,25 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">1 44 1
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2481,7 +2464,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2523,7 +2506,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9953
+          <t xml:space="preserve">593
 </t>
         </is>
       </c>
@@ -2535,7 +2518,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2547,13 +2530,13 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -2578,13 +2561,13 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02688
+          <t xml:space="preserve">03618
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14281
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2602,13 +2585,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4814
+          <t xml:space="preserve">24814
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1908
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2618,40 +2601,33 @@
 </t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+      <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">833
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14659
-</t>
+          <t>659</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2662,55 +2638,53 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>71603</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 29
+</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">831
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">869
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0169
-</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3114
-</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99208
-</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1018
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">969
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1087
-</t>
-        </is>
-      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46584
+          <t xml:space="preserve">4584
 </t>
         </is>
       </c>
@@ -2741,19 +2715,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8816
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120117
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2766,7 +2740,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2777,7 +2751,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2789,13 +2763,13 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2807,7 +2781,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2831,7 +2805,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7884
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -2849,7 +2823,7 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">1294
 </t>
         </is>
       </c>
@@ -2861,13 +2835,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2886,13 +2860,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29546
+          <t xml:space="preserve">2546
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2771
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -2902,39 +2876,32 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2209
-</t>
-        </is>
-      </c>
+      <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">1867
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -2946,25 +2913,25 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2868
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1883
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2976,25 +2943,24 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141487
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
@@ -3012,19 +2978,19 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -3043,7 +3009,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -3061,118 +3027,118 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8288
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8881
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
 </t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2080
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">736
@@ -3181,7 +3147,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3198,12 +3164,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">534
-</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -3216,15 +3177,10 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+      <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3242,7 +3198,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0219
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -3254,8 +3210,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3266,7 +3221,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3296,15 +3251,11 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -3356,13 +3307,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18246
+          <t xml:space="preserve">12546
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018
+          <t xml:space="preserve">2881
 </t>
         </is>
       </c>
@@ -3380,19 +3331,19 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3404,13 +3355,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -3422,7 +3373,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -3458,13 +3409,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3537,13 +3488,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106 2
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3555,7 +3506,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3579,13 +3530,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -3609,13 +3560,13 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3627,13 +3578,13 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3651,7 +3602,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3668,15 +3619,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3687,7 +3633,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3711,39 +3657,36 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691
-</t>
+          <t>469</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -3754,7 +3697,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -3766,46 +3709,40 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2991
+          <t xml:space="preserve">3931
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100
-</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">416
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3821,7 +3758,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23097
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -3833,37 +3770,35 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 051
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2541
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">9291
 </t>
         </is>
       </c>
@@ -3882,7 +3817,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3912,14 +3847,13 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3930,26 +3864,26 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211834
+          <t xml:space="preserve">1211834
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="n"/>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3990,33 +3924,17 @@
 </t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -4032,32 +3950,27 @@
 </t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -4099,13 +4012,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4124,7 +4037,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">3714
 </t>
         </is>
       </c>
@@ -4142,13 +4055,13 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4160,7 +4073,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8253
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4172,13 +4085,13 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4190,31 +4103,30 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">2327
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2416
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4238,7 +4150,7 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -4293,7 +4205,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4310,8 +4222,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4328,27 +4239,23 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">930
@@ -4357,7 +4264,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -4369,7 +4276,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4379,14 +4286,10 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t>6364</t>
-        </is>
-      </c>
+      <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4410,7 +4313,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">8386
 </t>
         </is>
       </c>
@@ -4447,125 +4350,121 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 8
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1028
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">933
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8408
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2068
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">775
 </t>
         </is>
       </c>
@@ -4590,13 +4489,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">23436
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4608,14 +4507,13 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">101 4
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4638,24 +4536,28 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -4670,19 +4572,19 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4706,7 +4608,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2069
 </t>
         </is>
       </c>
@@ -4737,61 +4639,50 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1869
-</t>
+          <t>788</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7009
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8939
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
@@ -4803,14 +4694,13 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 10
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14249
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4821,32 +4711,31 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81094
+          <t xml:space="preserve">21094
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">16818
 </t>
         </is>
       </c>
@@ -4858,20 +4747,14 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9998
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1161
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">999
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n"/>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>004</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4895,13 +4778,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12862
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4913,7 +4795,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111001
+          <t xml:space="preserve">11100
 </t>
         </is>
       </c>
@@ -4925,31 +4807,31 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 9
+          <t xml:space="preserve">2 9
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11721
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101208101
+          <t xml:space="preserve">10218101
 </t>
         </is>
       </c>
@@ -4962,7 +4844,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4974,13 +4856,13 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 66
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4992,13 +4874,13 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">611
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -5045,15 +4927,10 @@
 </t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
+      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -5065,31 +4942,31 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5101,31 +4978,31 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5137,37 +5014,37 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12064
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0081
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -5179,7 +5056,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5198,7 +5075,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
@@ -5216,13 +5093,13 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -5234,16 +5111,10 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">58
@@ -5258,31 +5129,31 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5312,13 +5183,13 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5336,7 +5207,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5385,7 +5256,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1656
 </t>
         </is>
       </c>
@@ -5397,15 +5268,11 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">397
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -5414,19 +5281,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -5438,8 +5305,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -5448,12 +5314,7 @@
 </t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
+      <c r="S34" s="3" t="n"/>
       <c r="T34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">748
@@ -5462,13 +5323,13 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5492,7 +5353,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5553,7 +5414,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5571,17 +5432,18 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5599,7 +5461,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -5617,7 +5479,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5641,13 +5503,13 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">895
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2441
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5696,7 +5558,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -5708,7 +5570,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -5733,13 +5595,13 @@
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5757,7 +5619,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5775,13 +5637,13 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2808
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5799,7 +5661,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5818,25 +5680,25 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16402
+          <t xml:space="preserve">16452
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16211
+          <t xml:space="preserve">11828
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13011
+          <t xml:space="preserve">16091
 </t>
         </is>
       </c>
@@ -5848,25 +5710,24 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">7106
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16006
+          <t xml:space="preserve">1606
 </t>
         </is>
       </c>
@@ -5876,39 +5737,34 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+      <c r="M37" s="3" t="n"/>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">18123
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -5920,12 +5776,13 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t xml:space="preserve">2894
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1942
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
@@ -5937,14 +5794,13 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44817
+          <t xml:space="preserve">4188
 </t>
         </is>
       </c>
@@ -5962,17 +5818,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12928
+</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2631
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8661
-</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -5983,13 +5843,13 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -6001,7 +5861,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">331
 </t>
         </is>
       </c>
@@ -6038,13 +5898,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2122
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117 8
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -6056,37 +5915,32 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7711
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1464
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">771
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -6106,8 +5960,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
-</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6124,7 +5977,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -6149,26 +6002,26 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1077
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -6186,13 +6039,13 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -6233,7 +6086,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53590
+          <t xml:space="preserve">3590
 </t>
         </is>
       </c>
@@ -6251,7 +6104,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01116
+          <t xml:space="preserve">01816
 </t>
         </is>
       </c>
@@ -6264,7 +6117,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6274,7 +6127,12 @@
 </t>
         </is>
       </c>
-      <c r="K40" s="3" t="n"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -6295,73 +6153,72 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">862
 </t>
         </is>
       </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -6380,7 +6237,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>48664</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -6397,7 +6254,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -6405,13 +6262,13 @@
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -6423,7 +6280,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -6435,25 +6292,25 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
@@ -6521,7 +6378,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9426
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6539,7 +6396,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6551,14 +6408,14 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6582,7 +6439,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -6594,25 +6451,25 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8299
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -6622,12 +6479,7 @@
 </t>
         </is>
       </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+      <c r="U42" s="3" t="n"/>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -6642,13 +6494,13 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -6671,16 +6523,21 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8109
+          <t xml:space="preserve">809
 </t>
         </is>
       </c>
@@ -6692,31 +6549,31 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0914
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6735,7 +6592,7 @@
       <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
+          <t xml:space="preserve">4055
 </t>
         </is>
       </c>
@@ -6747,19 +6604,19 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 16
+          <t xml:space="preserve">10 9
 </t>
         </is>
       </c>
@@ -6771,7 +6628,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">556
 </t>
         </is>
       </c>
@@ -6781,21 +6638,16 @@
 </t>
         </is>
       </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2193
-</t>
-        </is>
-      </c>
+      <c r="W43" s="3" t="n"/>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201 10
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 067
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6899,19 +6751,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6923,7 +6775,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -6941,22 +6793,22 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">660
@@ -6989,7 +6841,7 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -7022,31 +6874,31 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -7070,33 +6922,28 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14107
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7108,22 +6955,17 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n"/>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -746,13 +746,13 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -788,19 +788,19 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">0168
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">2900
 </t>
         </is>
       </c>
@@ -824,7 +824,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -836,13 +836,13 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -864,11 +864,7 @@
 </t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -884,13 +880,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94326
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>986</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -901,19 +897,18 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02150
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
+          <t xml:space="preserve">11210
 </t>
         </is>
       </c>
@@ -931,7 +926,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -943,19 +938,19 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
@@ -985,13 +980,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -1009,7 +1004,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -1019,7 +1014,12 @@
 </t>
         </is>
       </c>
-      <c r="Z5" s="3" t="n"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4844
+          <t xml:space="preserve">4944
 </t>
         </is>
       </c>
@@ -1060,13 +1060,13 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1096,11 +1096,16 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
@@ -1145,13 +1150,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1163,7 +1168,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1186,12 +1191,7 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1281
-</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
@@ -1218,13 +1218,14 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1247,13 +1248,14 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">898
+</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1282,7 +1284,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1306,19 +1308,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1337,7 +1339,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602
+          <t xml:space="preserve">4602
 </t>
         </is>
       </c>
@@ -1403,7 +1405,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1415,7 +1417,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1469,13 +1471,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1494,18 +1496,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t xml:space="preserve">22404
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18248
+          <t xml:space="preserve">1420
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">8291
 </t>
         </is>
       </c>
@@ -1517,13 +1520,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">2591
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">6717
 </t>
         </is>
       </c>
@@ -1547,8 +1550,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1557,15 +1559,10 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">3433
 </t>
         </is>
       </c>
@@ -1577,17 +1574,22 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">12721
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0912
-</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n"/>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1243
+</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1602,31 +1604,31 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">927
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">638
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4451
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1628
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4458
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -1651,35 +1653,37 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2821
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -1691,27 +1695,23 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16878
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">906
@@ -1720,31 +1720,31 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">104 14
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
@@ -1756,11 +1756,16 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
@@ -1775,7 +1780,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">16 14
 </t>
         </is>
       </c>
@@ -1806,45 +1811,40 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8311
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
@@ -1859,7 +1859,8 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">85
+</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1868,27 +1869,22 @@
 </t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
+      <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -1900,25 +1896,25 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">28220
 </t>
         </is>
       </c>
@@ -1991,19 +1987,19 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
@@ -2021,7 +2017,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -2039,18 +2035,19 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>086</t>
+          <t xml:space="preserve">2222
+</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -2074,7 +2071,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2105,7 +2102,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23238
+          <t xml:space="preserve">3238
 </t>
         </is>
       </c>
@@ -2117,7 +2114,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -2129,7 +2126,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -2139,13 +2136,13 @@
 </t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -2160,18 +2157,28 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -2192,13 +2199,13 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2210,13 +2217,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2265,13 +2272,13 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">28211
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2281,15 +2288,10 @@
 </t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">1 2
 </t>
         </is>
       </c>
@@ -2313,7 +2315,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2355,7 +2357,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2373,13 +2375,13 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -2404,7 +2406,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
+          <t xml:space="preserve">3348
 </t>
         </is>
       </c>
@@ -2422,25 +2424,25 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">9085
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 44 1
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2452,7 +2454,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2470,7 +2472,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2488,7 +2490,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2500,7 +2502,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2512,7 +2514,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -2542,7 +2544,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -2561,19 +2563,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03618
+          <t xml:space="preserve">13618
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
@@ -2585,13 +2587,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24814
+          <t xml:space="preserve">4814
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2601,33 +2603,40 @@
 </t>
         </is>
       </c>
-      <c r="J16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">888
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">833
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t xml:space="preserve">14659
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2638,47 +2647,49 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">10893
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>71603</t>
+          <t xml:space="preserve">1043
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 29
+          <t xml:space="preserve">21166
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t xml:space="preserve">1998
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">351
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">9691
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">0987
 </t>
         </is>
       </c>
@@ -2688,12 +2699,7 @@
 </t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+      <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2709,13 +2715,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">23124
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">9401
 </t>
         </is>
       </c>
@@ -2727,11 +2733,16 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">146
@@ -2740,7 +2751,8 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2751,40 +2763,40 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
@@ -2793,19 +2805,19 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691
+          <t xml:space="preserve">21891
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">7891
 </t>
         </is>
       </c>
@@ -2817,25 +2829,25 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">12116
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">28 12 1
 </t>
         </is>
       </c>
@@ -2860,7 +2872,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2546
+          <t xml:space="preserve">3546
 </t>
         </is>
       </c>
@@ -2876,10 +2888,15 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2909
+</t>
+        </is>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2891,7 +2908,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2901,13 +2918,13 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2919,7 +2936,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2937,13 +2954,13 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2960,37 +2977,37 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">224 884
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 11
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -3009,7 +3026,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">2194
 </t>
         </is>
       </c>
@@ -3027,7 +3044,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -3039,13 +3056,13 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3057,7 +3074,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3069,13 +3086,13 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3087,7 +3104,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8881
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3099,13 +3116,13 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2086
 </t>
         </is>
       </c>
@@ -3117,7 +3134,7 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3141,13 +3158,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">736
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3164,10 +3181,14 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">9268
 </t>
         </is>
       </c>
@@ -3177,7 +3198,12 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">90
@@ -3192,25 +3218,25 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">531
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>491</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3221,7 +3247,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3251,11 +3277,16 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="n"/>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18918
+</t>
+        </is>
+      </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -3307,14 +3338,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12546
+          <t xml:space="preserve">22842
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
-</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3331,19 +3361,19 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3355,7 +3385,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3373,7 +3403,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3389,12 +3419,7 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+      <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -3409,13 +3434,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3470,7 +3495,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
@@ -3482,7 +3507,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -3506,7 +3531,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -3518,7 +3543,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -3530,7 +3555,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3566,7 +3591,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">7240
 </t>
         </is>
       </c>
@@ -3602,7 +3627,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3619,10 +3644,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15426
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">1376
+</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3633,19 +3664,19 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">3526
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
@@ -3657,65 +3688,56 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81158
+          <t xml:space="preserve">2158
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3931
+          <t xml:space="preserve">2931
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -3727,22 +3749,28 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t xml:space="preserve">1109
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">6068
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3770,60 +3798,66 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">1701
+</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">11848
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9291
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9381
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3847,13 +3881,14 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t xml:space="preserve">787
+</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3864,7 +3899,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3876,14 +3911,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211834
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="n"/>
+          <t xml:space="preserve">881811
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -3902,8 +3942,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
-</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3924,17 +3963,23 @@
 </t>
         </is>
       </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t xml:space="preserve">156
+</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -3946,11 +3991,16 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
           <t>94</t>
@@ -3958,19 +4008,19 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -3988,37 +4038,37 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5117
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5514
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2544
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="Z25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4037,7 +4087,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3714
+          <t xml:space="preserve">3411
 </t>
         </is>
       </c>
@@ -4055,19 +4105,19 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4079,13 +4129,13 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4103,13 +4153,14 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>970</t>
+          <t xml:space="preserve">970
+</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4120,7 +4171,7 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2327
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -4132,7 +4183,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -4162,7 +4213,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4205,7 +4256,8 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4222,7 +4274,8 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t xml:space="preserve">160
+</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4239,13 +4292,13 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4255,7 +4308,12 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">930
@@ -4282,11 +4340,16 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">99
@@ -4307,13 +4370,13 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -4338,7 +4401,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4536
+          <t xml:space="preserve">453
 </t>
         </is>
       </c>
@@ -4348,12 +4411,7 @@
 </t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
+      <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4362,19 +4420,20 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 8
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4385,49 +4444,48 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8408
+          <t xml:space="preserve">8406
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4437,10 +4495,15 @@
 </t>
         </is>
       </c>
-      <c r="T28" s="3" t="n"/>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747
+</t>
+        </is>
+      </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4452,13 +4515,13 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">28641
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4470,7 +4533,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -4489,7 +4552,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
@@ -4501,19 +4564,20 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101 4
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>918</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4530,70 +4594,76 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8216
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">48
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4608,7 +4678,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4639,19 +4709,25 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>788</t>
+          <t xml:space="preserve">1788
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
+          <t xml:space="preserve">1384
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">1064
 </t>
         </is>
       </c>
@@ -4661,10 +4737,15 @@
 </t>
         </is>
       </c>
-      <c r="H30" s="3" t="n"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7107
+</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -4694,31 +4775,37 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14345
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">5 82
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
-</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="n"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2002
+</t>
+        </is>
+      </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21094
+          <t xml:space="preserve">1094
 </t>
         </is>
       </c>
@@ -4730,31 +4817,38 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">2303
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16818
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
+          <t xml:space="preserve">9981
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4161
+</t>
+        </is>
+      </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>004</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4772,30 +4866,31 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23577
+          <t xml:space="preserve">3577
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>963</t>
+          <t xml:space="preserve">9631
+</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11100
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -4807,44 +4902,44 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">8961
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 9
+          <t xml:space="preserve">28 9
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1721
+          <t xml:space="preserve">13721
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218101
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">4 90
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4856,7 +4951,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -4868,7 +4963,7 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
@@ -4880,31 +4975,31 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">401
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -4923,62 +5018,55 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n"/>
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">21 7
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">13 118
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -4994,15 +5082,10 @@
 </t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -5014,7 +5097,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">184415 18
 </t>
         </is>
       </c>
@@ -5026,37 +5109,37 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1169
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5093,7 +5176,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">2251
 </t>
         </is>
       </c>
@@ -5111,10 +5194,15 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n"/>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">58
@@ -5129,25 +5217,25 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -5177,13 +5265,13 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -5201,13 +5289,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">2865
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5226,7 +5314,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23502
+          <t xml:space="preserve">3502
 </t>
         </is>
       </c>
@@ -5250,50 +5338,55 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -5305,7 +5398,8 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -5314,7 +5408,12 @@
 </t>
         </is>
       </c>
-      <c r="S34" s="3" t="n"/>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">748
@@ -5323,7 +5422,7 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -5353,7 +5452,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -5396,7 +5495,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -5426,24 +5525,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5461,46 +5561,46 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1281
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">895
@@ -5509,7 +5609,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5528,7 +5628,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3568
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -5558,7 +5658,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -5570,7 +5670,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -5592,10 +5692,15 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -5625,7 +5730,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">1682
 </t>
         </is>
       </c>
@@ -5637,13 +5742,13 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2808
+          <t xml:space="preserve">8208
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5661,7 +5766,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -5680,25 +5785,25 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16452
+          <t xml:space="preserve">1643
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11828
+          <t xml:space="preserve">2314
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16091
+          <t xml:space="preserve">1071
 </t>
         </is>
       </c>
@@ -5716,95 +5821,101 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n"/>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">8998
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">0120
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18123
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1038
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
+          <t xml:space="preserve">93834
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="n"/>
+          <t xml:space="preserve">9231
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">029
+</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4188
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+          <t xml:space="preserve">2187
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5820,30 +5931,31 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12928
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t xml:space="preserve">1661
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5853,40 +5965,40 @@
 </t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
+      <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">331
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">16889
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5898,18 +6010,19 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">02251
+</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">20971
 </t>
         </is>
       </c>
@@ -5919,32 +6032,42 @@
 </t>
         </is>
       </c>
-      <c r="U38" s="3" t="n"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1904
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2005
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">89718
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5960,80 +6083,78 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t xml:space="preserve">2644
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>331</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -6045,31 +6166,36 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">744
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="n"/>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -6086,56 +6212,61 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01816
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n"/>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
@@ -6147,78 +6278,79 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">744
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6237,129 +6369,138 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t xml:space="preserve">3590
+</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10169
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2094
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="n"/>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -6378,44 +6519,43 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
-</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -6427,7 +6567,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -6439,68 +6579,73 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">6820
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">555
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -6525,133 +6670,143 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">7426
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">2885
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">1880
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="n"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 9
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">555
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">556
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="n"/>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2185
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6709,143 +6864,143 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3629
+          <t xml:space="preserve">18890
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1344
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1081
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">697
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 9
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">14055
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">12684
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">3300
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">556
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">1088
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6859,115 +7014,149 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3629
+</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1659
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -728,140 +728,117 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
-</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Z4" s="3" t="n"/>
@@ -880,8 +857,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -891,8 +867,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -902,122 +877,102 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1035,141 +990,118 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4944
-</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1187,141 +1119,118 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3844
-</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1339,146 +1248,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1496,56 +1381,47 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
-</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6717
-</t>
+          <t>677</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1555,81 +1431,68 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3433
-</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12721
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3842
-</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">927
-</t>
+          <t>927</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>031</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4451
-</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1647,141 +1510,118 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
-</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104 14
-</t>
+          <t>101 14</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">769
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 14
-</t>
+          <t>21 14</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1799,44 +1639,37 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996
-</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1847,87 +1680,73 @@
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1945,146 +1764,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2102,141 +1897,118 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3238
-</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
-</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2254,141 +2026,118 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
-</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2
-</t>
+          <t>21 2</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2406,146 +2155,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
-</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9085
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">593
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2563,140 +2288,117 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13618
-</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1099
-</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4814
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14659
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10893
-</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1043
-</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21166
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
-</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">351
-</t>
+          <t>351</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0987
-</t>
+          <t>097</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4584
-</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="Z16" s="3" t="n"/>
@@ -2715,146 +2417,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23124
-</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9401
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21891
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7891
-</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12116
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 12 1
-</t>
+          <t>28 8 1</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2872,38 +2550,32 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3546
-</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2918,38 +2590,32 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2959,56 +2625,47 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 884
-</t>
+          <t>224 214</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 11
-</t>
+          <t>28 12</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3026,146 +2683,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>731</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3188,32 +2821,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -3223,104 +2851,87 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18918
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3338,8 +2949,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22842
-</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3349,129 +2959,108 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>968</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3489,146 +3078,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3392
-</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3646,56 +3211,47 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15426
-</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
-</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3526
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3705,14 +3261,12 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3725,50 +3279,42 @@
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2158
-</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2931
-</t>
+          <t>937</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6068
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3786,56 +3332,47 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11848
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3845,86 +3382,72 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2101
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881811
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3947,58 +3470,49 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -4008,68 +3522,57 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
+          <t>555</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4087,146 +3590,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3411
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4244,146 +3723,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
-</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4401,51 +3856,43 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">453
-</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4455,86 +3902,72 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">747
-</t>
+          <t>747</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28641
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4552,146 +3985,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4709,146 +4118,122 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1788
-</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1064
-</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7107
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14345
-</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 82
-</t>
+          <t>2 89</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002
-</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>999</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4866,141 +4251,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3577
-</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9631
-</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8961
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13721
-</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 90
-</t>
+          <t>12 90</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5023,38 +4385,32 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 7
-</t>
+          <t>21 7</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 118
-</t>
+          <t>13 15</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="3" t="n"/>
@@ -5066,81 +4422,68 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184415 18
-</t>
+          <t>158 8</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5158,38 +4501,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2251
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5199,104 +4536,87 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
-</t>
+          <t>774</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2865
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5314,146 +4634,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3502
-</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5471,146 +4767,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688
-</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
-</t>
+          <t>895</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5628,146 +4900,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8208
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5785,44 +5033,37 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643
-</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7106
-</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J37" s="3" t="n"/>
@@ -5833,87 +5074,73 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93834
-</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
+          <t>029</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187
-</t>
+          <t>487</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5931,141 +5158,118 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16889
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02251
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20971
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904
-</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
-</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89718
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6083,8 +5287,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644
-</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6094,27 +5297,23 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -6124,8 +5323,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -6135,65 +5333,55 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="Z39" s="3" t="n"/>
@@ -6212,146 +5400,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
-</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6369,8 +5533,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
-</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -6380,99 +5543,83 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10169
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2094
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
@@ -6482,26 +5629,22 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6524,135 +5667,113 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6820
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
+          <t>579</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6670,141 +5791,118 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7426
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2885
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">555
-</t>
+          <t>555</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2185
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6822,8 +5920,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6864,141 +5961,118 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18890
-</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
-</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">697
-</t>
+          <t>697</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14055
-</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12684
-</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300
-</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">556
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>012</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
-</t>
+          <t>087</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7016,32 +6090,27 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3629
-</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -7051,110 +6120,92 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1659
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>101 14</t>
+          <t>01 214 1</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>21 14</t>
+          <t>181 14</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>21 2</t>
+          <t>1 21 2</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2492,17 +2492,17 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>28 8 1</t>
+          <t>20 2 2</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>224 214</t>
+          <t>226 214</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>28 12</t>
+          <t>14 214</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>195</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>282</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>3 9</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>12 90</t>
+          <t>21 90</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>204</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>13 15</t>
+          <t>13 01</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>158 8</t>
+          <t>2611 4</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5119,28 +5119,28 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>0294</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -5249,27 +5249,27 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>183</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>734</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>011</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>114</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>01</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/905/original_transcribed_data.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>01 214 1</t>
+          <t>04 20</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>181 14</t>
+          <t>00 04</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>09</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1 21 2</t>
+          <t>21 2</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>20 2 2</t>
+          <t>20 0 1</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>226 214</t>
+          <t>800 00</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>14 214</t>
+          <t>18 20</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>840</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>2 89</t>
+          <t>8 89</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>392</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>00</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>13 01</t>
+          <t>13 00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>2611 4</t>
+          <t>000 2</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>187</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5125,12 +5125,12 @@
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>923</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>0294</t>
+          <t>029</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>820</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>896</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6170,17 +6170,17 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
